--- a/docs/CD13-translation-review.xlsx
+++ b/docs/CD13-translation-review.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,15 @@
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00BE123C"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +105,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -162,6 +174,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E23"/>
+  <dimension ref="B1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -648,6 +670,95 @@
       <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Strings extracted 2026-08-24 from src/data/slipFlagLines.js, src/data/screeningChips.js and src/components/AuraChat.jsx on branch aura. Back-translations from TRANSLATION-BRIEF.md, machine-produced and unverified. The ten slip lines have no back-translation on file; review them directly against the English. Sheet prepared with AI assistance; a named person must verify corrections against the app before they ship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>GROUP 5 — added 2026-09-13. Three MORE strings, and they are not like the other nineteen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The nineteen above are questions and observations. A mistranslation there collects a wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>answer, which is bad and recoverable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The three in Group 5 are PROHIBITIONS. Their whole job is to stop somebody doing something,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>and a prohibition degrades in a way nothing else here does: "do not try this on your own" can</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>come back as "you may prefer to have someone with you" and read perfectly naturally. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sentence is fine. The instruction is gone. A reviewer skimming for accuracy passes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>SO THE ONE THING TO CHECK IN GROUP 5 IS THAT EACH IS STILL AN INSTRUCTION, NOT A SUGGESTION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Everything else is secondary. About five minutes per language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>These three are enforced in code: the build fails until a reviewer is named for each language</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>in src/data/copyReview.js, or an owner signs a dated waiver. Nothing ships past them.</t>
         </is>
       </c>
     </row>
@@ -662,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1449,6 +1560,118 @@
         </is>
       </c>
       <c r="C26" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>GROUP 5 — SAFETY-CRITICAL. These three BLOCK THE BUILD until reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>measures.doNotSelfTest</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Chat and form — shown ABOVE both strength questions, before either test is described. Also the first thing on the strength block of the printed report.</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Please do not try either test on your own now. These are measured with someone there to help.</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Sila jangan cuba mana-mana ujian ini sendiri sekarang. Ujian ini diukur dengan ada orang di sisi untuk membantu.</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Please do not try any of these tests by yourself now. These tests are measured with someone at your side to help.</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS A PROHIBITION. If your back-translation contains "should", "may prefer", "it is better to", or any suggestion rather than an instruction NOT to do it, the string has failed even if it reads beautifully. This is the one that stops a 78-year-old attempting a timed chair stand alone.</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr"/>
+      <c r="I29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>measures.noComparison</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Chat and printed report — shown when no published range covers the person’s age, instead of a band.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>We have kept your number so you can show it to your doctor. We do not have a published range that covers your age, so we are not going to guess one.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Kami telah simpan nombor anda supaya anda boleh tunjukkan kepada doktor anda. Kami tiada julat terbitan yang meliputi umur anda, jadi kami tidak akan meneka.</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>We have kept your number so that you can show it to your doctor. We do not have a published range that covers your age, so we will not guess.</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "WE DID NOT COMPARE IT". If it can be read as a comparison that came out badly, it has failed. The person kept a number; nothing was judged.</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr"/>
+      <c r="I30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>measures.notADiagnosis</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Printed report, page 3 — directly under the two measurements.</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. They are not a diagnosis, and they have not changed your result above.</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Nombor ini menerangkan kekuatan anda hari ini. Ia bukan diagnosis, dan ia tidak mengubah keputusan anda di atas.</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. It is not a diagnosis, and it does not change your result above.</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "NOT A DIAGNOSIS". Tamil note: the shipped Tamil uses நோய் கண்டறிதல் ("disease diagnosis"), which is narrower than the English. Confirm that register is right for somebody who is not unwell.</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr"/>
+      <c r="H31" s="17" t="inlineStr"/>
+      <c r="I31" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1466,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2476,118 @@
         </is>
       </c>
       <c r="C26" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>GROUP 5 — SAFETY-CRITICAL. These three BLOCK THE BUILD until reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>measures.doNotSelfTest</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Chat and form — shown ABOVE both strength questions, before either test is described. Also the first thing on the strength block of the printed report.</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Please do not try either test on your own now. These are measured with someone there to help.</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>请不要现在自己尝试这两项测试。这些测试要在有人在旁协助的情况下才进行测量。</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Please do not try these two tests by yourself now. These tests are only measured when there is someone alongside to assist.</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS A PROHIBITION. If your back-translation contains "should", "may prefer", "it is better to", or any suggestion rather than an instruction NOT to do it, the string has failed even if it reads beautifully. This is the one that stops a 78-year-old attempting a timed chair stand alone.</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr"/>
+      <c r="I29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>measures.noComparison</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Chat and printed report — shown when no published range covers the person’s age, instead of a band.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>We have kept your number so you can show it to your doctor. We do not have a published range that covers your age, so we are not going to guess one.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>我们保存了您的数字，方便您给医生看。我们没有涵盖您年龄的已发表范围，所以我们不会去猜测。</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>We have saved your number, so it is convenient for you to show your doctor. We do not have a published range covering your age, so we will not guess.</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "WE DID NOT COMPARE IT". If it can be read as a comparison that came out badly, it has failed. The person kept a number; nothing was judged.</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr"/>
+      <c r="I30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>measures.notADiagnosis</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Printed report, page 3 — directly under the two measurements.</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. They are not a diagnosis, and they have not changed your result above.</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>这些数字描述的是您今天的力量。它们不是诊断，也没有改变您上面的结果。</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. They are not a diagnosis, and they have not changed your result above.</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "NOT A DIAGNOSIS". Tamil note: the shipped Tamil uses நோய் கண்டறிதல் ("disease diagnosis"), which is narrower than the English. Confirm that register is right for somebody who is not unwell.</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr"/>
+      <c r="H31" s="17" t="inlineStr"/>
+      <c r="I31" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2270,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3058,6 +3393,118 @@
       </c>
       <c r="C26" s="13" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>GROUP 5 — SAFETY-CRITICAL. These three BLOCK THE BUILD until reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>measures.doNotSelfTest</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Chat and form — shown ABOVE both strength questions, before either test is described. Also the first thing on the strength block of the printed report.</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Please do not try either test on your own now. These are measured with someone there to help.</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>இந்த இரண்டு சோதனைகளையும் இப்போது நீங்களே தனியாக முயற்சிக்க வேண்டாம். உதவிக்கு ஒருவர் உடன் இருக்கும்போது மட்டுமே இவை அளக்கப்படுகின்றன.</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Do not attempt these two tests by yourself alone now. These are measured only when someone is with you to help.</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS A PROHIBITION. If your back-translation contains "should", "may prefer", "it is better to", or any suggestion rather than an instruction NOT to do it, the string has failed even if it reads beautifully. This is the one that stops a 78-year-old attempting a timed chair stand alone.</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr"/>
+      <c r="I29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>measures.noComparison</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Chat and printed report — shown when no published range covers the person’s age, instead of a band.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>We have kept your number so you can show it to your doctor. We do not have a published range that covers your age, so we are not going to guess one.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>உங்கள் மருத்துவரிடம் காட்டுவதற்காக உங்கள் எண்ணை நாங்கள் வைத்துள்ளோம். உங்கள் வயதை உள்ளடக்கிய வெளியிடப்பட்ட வரம்பு எங்களிடம் இல்லை, எனவே நாங்கள் ஊகிக்கப் போவதில்லை.</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>We have kept your number so that you can show it to your doctor. We do not have a published range that covers your age, so we are not going to guess.</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "WE DID NOT COMPARE IT". If it can be read as a comparison that came out badly, it has failed. The person kept a number; nothing was judged.</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr"/>
+      <c r="I30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>measures.notADiagnosis</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Printed report, page 3 — directly under the two measurements.</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. They are not a diagnosis, and they have not changed your result above.</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>இந்த எண்கள் இன்றைய உங்கள் வலிமையை விவரிக்கின்றன. இவை நோய் கண்டறிதல் அல்ல, மேலே உள்ள உங்கள் முடிவை இவை மாற்றவும் இல்லை.</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>These numbers describe your strength today. These are not a DISEASE diagnosis, and they have not changed your result above.</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>MUST READ AS "NOT A DIAGNOSIS". Tamil note: the shipped Tamil uses நோய் கண்டறிதல் ("disease diagnosis"), which is narrower than the English. Confirm that register is right for somebody who is not unwell.</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr"/>
+      <c r="H31" s="17" t="inlineStr"/>
+      <c r="I31" s="17" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Verdict" prompt="OK as is, or Needs change" type="list">
